--- a/habit_tracking_forms/029_voiding_diary_form--habit_tracking_forms.xlsx
+++ b/habit_tracking_forms/029_voiding_diary_form--habit_tracking_forms.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="settings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -872,7 +872,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Notes</t>
+          <t>Voiding Diary Notes</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -895,7 +895,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Phone</t>
+          <t>Voiding Diary Phone</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -918,7 +918,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Voiding Diary Email</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -936,12 +936,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>voiding_diary_comments</t>
+          <t>voiding_diary_comments_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Comments</t>
+          <t>Voiding Diary Comments 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
